--- a/Test Project/TestUI/document/LeThiThuyNhi.xlsx
+++ b/Test Project/TestUI/document/LeThiThuyNhi.xlsx
@@ -4,84 +4,315 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22488" windowHeight="9215"/>
+    <workbookView windowWidth="22488" windowHeight="9215" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TestScenario" sheetId="1" r:id="rId1"/>
-    <sheet name="Testdata" sheetId="2" r:id="rId2"/>
-    <sheet name="Testcase" sheetId="3" r:id="rId3"/>
+    <sheet name="Test data" sheetId="2" r:id="rId2"/>
+    <sheet name="Test case" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="97">
   <si>
     <t>Scenario ID</t>
   </si>
   <si>
-    <t>Feature</t>
+    <t>Target Module</t>
   </si>
   <si>
     <t>Scenario Description</t>
   </si>
   <si>
-    <t>TS_01</t>
-  </si>
-  <si>
-    <t>Create Product</t>
-  </si>
-  <si>
-    <t>Verify the ability to add new products with valid and invalid data.</t>
-  </si>
-  <si>
-    <t>TS_02</t>
-  </si>
-  <si>
-    <t>Product Listing</t>
-  </si>
-  <si>
-    <t>Verify the display, filtering, and pagination of the product list.</t>
-  </si>
-  <si>
-    <t>TS_03</t>
-  </si>
-  <si>
-    <t>Product Actions</t>
-  </si>
-  <si>
-    <t>Verify secondary actions like viewing details and toggling status.</t>
-  </si>
-  <si>
-    <t>TS_04</t>
-  </si>
-  <si>
-    <t>Data Import</t>
-  </si>
-  <si>
-    <t>Verify the Excel template download and data import validation.</t>
-  </si>
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Field Name</t>
-  </si>
-  <si>
-    <t>Input Data Value</t>
+    <t>TS_PROD_01</t>
+  </si>
+  <si>
+    <t>Product Management</t>
+  </si>
+  <si>
+    <t>Validate core CRUD operations including valid product creation, duplicate SKU prevention, and negative price handling.</t>
+  </si>
+  <si>
+    <t>TS_PROD_02</t>
+  </si>
+  <si>
+    <t>Verify listing interactions, including viewing details, toggling trending status, searching, and pagination.</t>
+  </si>
+  <si>
+    <t>TS_PROD_03</t>
+  </si>
+  <si>
+    <t>Validate the Excel Import/Export functionality, ensuring proper template downloading and robust error handling for empty or invalid file formats.</t>
   </si>
   <si>
     <t>Data Type</t>
   </si>
   <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Payload / Value</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Valid Product Data</t>
+  </si>
+  <si>
+    <t>SKU, Name, Cost, Sale</t>
+  </si>
+  <si>
+    <r>
+      <t>AUTO-SKU-100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Laptop Gaming Auto Test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15000000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20000000</t>
+    </r>
+  </si>
+  <si>
+    <t>Standard data for successful creation.</t>
+  </si>
+  <si>
+    <t>Duplicate Data</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>AUTO-SKU-100</t>
+  </si>
+  <si>
+    <t>Test unique constraints on the SKU field.</t>
+  </si>
+  <si>
+    <t>Negative Number</t>
+  </si>
+  <si>
+    <t>CostPrice</t>
+  </si>
+  <si>
+    <t>Test HTML5/Backend validation for negative pricing.</t>
+  </si>
+  <si>
+    <t>Search String</t>
+  </si>
+  <si>
+    <r>
+      <t>Search Box (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>AUTO-SKU</t>
+  </si>
+  <si>
+    <t>Test search functionality.</t>
+  </si>
+  <si>
+    <t>Invalid File Type</t>
+  </si>
+  <si>
+    <t>File Upload</t>
+  </si>
+  <si>
+    <r>
+      <t>test_error_import.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> containing "Đây không phải là file Excel!"</t>
+    </r>
+  </si>
+  <si>
+    <t>Test backend validation for correct file extensions (.xlsx/.xls) during import.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Pre-conditions</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>TC_PROD_01</t>
   </si>
   <si>
-    <t>SKU / Name / Cost</t>
-  </si>
-  <si>
-    <r>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Create a valid product</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">User is on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.../Admin/Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click "Create". 
+2. Enter valid SKU, Name, Categories, and Prices. 
+3. Click Submit.</t>
+  </si>
+  <si>
+    <t>System saves the product and displays it in the list.</t>
+  </si>
+  <si>
+    <t>Created successfully.</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>TC_PROD_02</t>
+  </si>
+  <si>
+    <t>Prevent creation with duplicate SKU</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">User is on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.../Admin/Products/Create</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Enter an already existing SKU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>AUTO-SKU-100</t>
     </r>
     <r>
@@ -91,7 +322,27 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
+      <t>). 
+2. Fill other required fields. 
+3. Click Submit.</t>
+    </r>
+  </si>
+  <si>
+    <t>System blocks creation and shows a "SKU already exists" error.</t>
+  </si>
+  <si>
+    <t>System successfully blocked duplicate SKU.</t>
+  </si>
+  <si>
+    <t>TC_PROD_03</t>
+  </si>
+  <si>
+    <t>Prevent negative values in Cost Price</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter valid SKU and Name. 
+2. Enter </t>
     </r>
     <r>
       <rPr>
@@ -100,7 +351,7 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>Laptop Gaming</t>
+      <t>-50000</t>
     </r>
     <r>
       <rPr>
@@ -109,7 +360,59 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
+      <t xml:space="preserve"> into Cost Price. 
+3. Click Submit.</t>
+    </r>
+  </si>
+  <si>
+    <t>Form validation prevents submission, showing an error for invalid price.</t>
+  </si>
+  <si>
+    <t>HTML5 UI blocked saving negative price.</t>
+  </si>
+  <si>
+    <t>TC_PROD_04</t>
+  </si>
+  <si>
+    <t>View product details</t>
+  </si>
+  <si>
+    <t>1. Click the 'Details' button for a product. 
+2. View data and navigate back.</t>
+  </si>
+  <si>
+    <t>System navigates to the Details page displaying correct information.</t>
+  </si>
+  <si>
+    <t>Accessed Details page successfully.</t>
+  </si>
+  <si>
+    <t>TC_PROD_05</t>
+  </si>
+  <si>
+    <t>Toggle Trending status</t>
+  </si>
+  <si>
+    <t>1. Click the 'Trending' toggle button for a product.</t>
+  </si>
+  <si>
+    <t>System successfully updates the trending status via AJAX.</t>
+  </si>
+  <si>
+    <t>Trending toggle button not found on the UI.</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
+    <t>TC_PROD_06</t>
+  </si>
+  <si>
+    <t>Search for a product</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Enter </t>
     </r>
     <r>
       <rPr>
@@ -118,21 +421,7 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>15000000</t>
-    </r>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>TC_PROD_02</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <r>
-      <t>AUTO-SKU-100</t>
+      <t>AUTO-SKU</t>
     </r>
     <r>
       <rPr>
@@ -141,150 +430,141 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> (Existing)</t>
-    </r>
-  </si>
-  <si>
-    <t>Duplicate</t>
-  </si>
-  <si>
-    <t>TC_PROD_03</t>
-  </si>
-  <si>
-    <t>CostPrice</t>
-  </si>
-  <si>
-    <t>Invalid (Negative)</t>
-  </si>
-  <si>
-    <t>TC_PROD_06</t>
-  </si>
-  <si>
-    <t>Search Query</t>
-  </si>
-  <si>
-    <t>AUTO-SKU</t>
-  </si>
-  <si>
-    <t>String</t>
+      <t xml:space="preserve"> into the search box. 
+2. Click the 'Tìm kiếm' button.</t>
+    </r>
+  </si>
+  <si>
+    <t>Grid updates to show only products matching the search term.</t>
+  </si>
+  <si>
+    <t>Search completed successfully.</t>
   </si>
   <si>
     <t>TC_PROD_07</t>
   </si>
   <si>
-    <t>pageSize</t>
-  </si>
-  <si>
-    <t>Numeric</t>
+    <t>Change page size</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Select </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> from the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>pageSize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> dropdown.</t>
+    </r>
+  </si>
+  <si>
+    <t>Page reloads displaying 25 records per page.</t>
+  </si>
+  <si>
+    <t>Page size dropdown not found on the UI.</t>
+  </si>
+  <si>
+    <t>TC_PROD_08</t>
+  </si>
+  <si>
+    <t>Download Excel Template</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">User is on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.../Admin/Products/ImportExcel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click the download template link/button.</t>
+  </si>
+  <si>
+    <t>Browser successfully downloads the predefined Excel template.</t>
+  </si>
+  <si>
+    <t>Template downloaded successfully.</t>
+  </si>
+  <si>
+    <t>TC_PROD_09</t>
+  </si>
+  <si>
+    <t>Import Excel with empty file</t>
+  </si>
+  <si>
+    <t>1. Leave the file input empty. 
+2. Click the 'Preview' submit button.</t>
+  </si>
+  <si>
+    <t>System blocks the request and prompts the user to select a file.</t>
+  </si>
+  <si>
+    <t>Browser blocked upload (Required validation).</t>
   </si>
   <si>
     <t>TC_PROD_10</t>
   </si>
   <si>
-    <t>Upload File</t>
-  </si>
-  <si>
-    <t>test_error_import.txt</t>
-  </si>
-  <si>
-    <t>Invalid Extension</t>
-  </si>
-  <si>
-    <t>Test Case Name</t>
-  </si>
-  <si>
-    <t>Step Description</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Create Valid Product</t>
-  </si>
-  <si>
-    <t>1. Go to Create page. 
-2. Input valid data. 
-3. Click Submit.</t>
-  </si>
-  <si>
-    <t>System saves product and redirects to Index.</t>
-  </si>
-  <si>
-    <t>Duplicate SKU</t>
-  </si>
-  <si>
-    <t>1. Use an existing SKU. 
-2. Fill other fields. 
-3. Click Submit.</t>
-  </si>
-  <si>
-    <t>System blocks submission and shows "Duplicate SKU" error.</t>
-  </si>
-  <si>
-    <t>Negative Price</t>
-  </si>
-  <si>
-    <t>1. Input -50000 in Cost Price. 
-2. Click Submit.</t>
-  </si>
-  <si>
-    <t>System displays validation error; prevents negative values.</t>
-  </si>
-  <si>
-    <t>TC_PROD_04</t>
-  </si>
-  <si>
-    <t>View Details</t>
-  </si>
-  <si>
-    <t>1. Click "Details" icon on a product row.</t>
-  </si>
-  <si>
-    <t>System opens product detail view correctly.</t>
-  </si>
-  <si>
-    <t>TC_PROD_05</t>
-  </si>
-  <si>
-    <t>Toggle Trending</t>
-  </si>
-  <si>
-    <t>1. Click the Trending toggle button.</t>
-  </si>
-  <si>
-    <t>Status updates via AJAX without page reload.</t>
-  </si>
-  <si>
-    <t>Search Product</t>
-  </si>
-  <si>
-    <t>1. Type keyword in search box. 
-2. Click Search.</t>
-  </si>
-  <si>
-    <t>List filters to show only matching products.</t>
-  </si>
-  <si>
-    <t>Change Page Size</t>
-  </si>
-  <si>
-    <t>1. Select "25" from Page Size dropdown.</t>
-  </si>
-  <si>
-    <t>Grid refreshes to show 25 rows per page.</t>
-  </si>
-  <si>
-    <t>TC_PROD_08</t>
-  </si>
-  <si>
-    <t>Download Template</t>
-  </si>
-  <si>
-    <t>1. Click "Export Template" link.</t>
-  </si>
-  <si>
-    <r>
-      <t>Product_Template.xlsx</t>
+    <t>Import invalid file format (.txt)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Upload a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.txt</t>
     </r>
     <r>
       <rPr>
@@ -293,50 +573,15 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> is downloaded successfully.</t>
-    </r>
-  </si>
-  <si>
-    <t>TC_PROD_09</t>
-  </si>
-  <si>
-    <t>Import Empty File</t>
-  </si>
-  <si>
-    <t>1. Click "Preview" without selecting a file.</t>
-  </si>
-  <si>
-    <t>Browser or System prompts "File is required."</t>
-  </si>
-  <si>
-    <t>Invalid File Type</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Upload a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> file. 
-2. Click Preview.</t>
-    </r>
-  </si>
-  <si>
-    <t>System displays "Invalid file format" error.</t>
+      <t xml:space="preserve"> file instead of Excel. 
+2. Click the 'Preview' button.</t>
+    </r>
+  </si>
+  <si>
+    <t>Backend catches the invalid format and displays an error without crashing.</t>
+  </si>
+  <si>
+    <t>Uploaded invalid file; backend successfully caught the error.</t>
   </si>
 </sst>
 </file>
@@ -345,9 +590,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -378,7 +623,84 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,82 +714,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -485,7 +731,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,7 +745,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -508,7 +753,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -530,6 +775,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -542,67 +817,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,67 +937,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,24 +950,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -724,32 +969,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF1F1F1F"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1F1F1F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF1F1F1F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1F1F1F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,15 +1010,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -809,6 +1030,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,12 +1072,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -859,134 +1104,134 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -997,18 +1242,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1333,65 +1587,59 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="33.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="13.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="51.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.55" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="28.35" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="41.4" spans="1:3">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="28.35" spans="1:3">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="27.6" spans="1:3">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+    </row>
+    <row r="4" ht="41.4" spans="1:3">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="28.35" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="28.35" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>14</v>
-      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1402,111 +1650,97 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="19.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="19.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="41.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="22.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="18.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="45.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="59.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.55" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="27.6" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" ht="14.55" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" ht="14.55" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="5">
+        <v>-50000</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" ht="14.55" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="6">
-        <v>-50000</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="6" ht="27.6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" ht="14.55" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="14.55" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="6">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" ht="14.55" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1518,201 +1752,303 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="19.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="54.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="7.88888888888889" customWidth="1"/>
+    <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="34.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="27.5555555555556" customWidth="1"/>
+    <col min="7" max="7" width="27.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="6.88888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.55" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" ht="55.2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" ht="42.15" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" ht="42.15" spans="1:5">
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="55.2" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" ht="28.35" spans="1:5">
+    </row>
+    <row r="4" ht="41.4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" ht="14.55" spans="1:5">
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="41.4" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" ht="14.55" spans="1:5">
+        <v>62</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" ht="27.6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="28.35" spans="1:5">
+        <v>67</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="41.4" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="14.55" spans="1:5">
+        <v>72</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" ht="27.6" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" ht="14.55" spans="1:5">
+        <v>78</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" ht="41.4" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" ht="14.55" spans="1:5">
+        <v>82</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" ht="41.4" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>88</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" ht="28.35" spans="1:5">
+        <v>89</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" ht="41.4" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
